--- a/AAII_Financials/Quarterly/CE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CE_QTR_FIN.xlsx
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2752000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2337000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2204000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2419000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2532000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2389000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2358000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2648000</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2611000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2569000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2723000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2795000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2853000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2348000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2301000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2486000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2538000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2275000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2266000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2198000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1798000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1591000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1411000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1460000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1432000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1586000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1592000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1687000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1689000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1771000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1844000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1851000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1593000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1566000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1510000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1471000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1311000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1323000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2134000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1850000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1770000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1898000</v>
       </c>
-      <c r="G9" s="3">
-        <v>2000000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1998000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1915000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1761000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2029000</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2057000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1956000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2050000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2109000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2222000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1964000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1755000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1781000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1793000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1554000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1551000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1437000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1313000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1215000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1084000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>951000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1112000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1116000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1172000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1234000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1269000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1255000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1323000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1180000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1183000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1145000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1121000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>989000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>968000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E10" s="3">
         <v>487000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>434000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>521000</v>
       </c>
-      <c r="G10" s="3">
-        <v>532000</v>
-      </c>
       <c r="H10" s="3">
+        <v>534000</v>
+      </c>
+      <c r="I10" s="3">
         <v>474000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>597000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>619000</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>554000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>613000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>673000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>686000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>631000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>384000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>546000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>705000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>745000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>721000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>715000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>761000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>485000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>376000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>327000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>242000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>348000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>316000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>414000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>423000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>453000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>420000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>516000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>521000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>515000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>413000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>383000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>365000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>350000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>322000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>355000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,19 +1249,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E12" s="3">
         <v>28000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>31000</v>
       </c>
       <c r="G12" s="3">
         <v>31000</v>
@@ -1260,61 +1274,61 @@
         <v>31000</v>
       </c>
       <c r="J12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K12" s="3">
         <v>32000</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>34000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>32000</v>
       </c>
       <c r="N12" s="3">
         <v>32000</v>
       </c>
       <c r="O12" s="3">
+        <v>32000</v>
+      </c>
+      <c r="P12" s="3">
         <v>40000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>42000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>37000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>22000</v>
-      </c>
-      <c r="X12" s="3">
-        <v>20000</v>
       </c>
       <c r="Y12" s="3">
         <v>20000</v>
       </c>
       <c r="Z12" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AA12" s="3">
         <v>19000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>18000</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>17000</v>
       </c>
       <c r="AC12" s="3">
         <v>17000</v>
@@ -1326,10 +1340,10 @@
         <v>17000</v>
       </c>
       <c r="AF12" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AG12" s="3">
         <v>16000</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>18000</v>
       </c>
       <c r="AH12" s="3">
         <v>18000</v>
@@ -1341,25 +1355,28 @@
         <v>18000</v>
       </c>
       <c r="AK12" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AL12" s="3">
         <v>20000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>19000</v>
-      </c>
-      <c r="AM12" s="3">
-        <v>17000</v>
       </c>
       <c r="AN12" s="3">
         <v>17000</v>
       </c>
       <c r="AO12" s="3">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="AP12" s="3">
         <v>20000</v>
       </c>
+      <c r="AQ12" s="3">
+        <v>20000</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1480,147 +1497,153 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>89000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1494000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>22000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>60000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1694000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>64000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>21000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-479000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>18000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-7000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>17000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-13000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>3000</v>
       </c>
       <c r="U14" s="3">
         <v>3000</v>
       </c>
       <c r="V14" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>3000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-1406000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>20000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>102000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>98000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>3000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>3000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>55000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="E15" s="3">
         <v>40000</v>
       </c>
       <c r="F15" s="3">
-        <v>42000</v>
+        <v>40000</v>
       </c>
       <c r="G15" s="3">
         <v>42000</v>
       </c>
       <c r="H15" s="3">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="I15" s="3">
         <v>40000</v>
@@ -1629,61 +1652,61 @@
         <v>40000</v>
       </c>
       <c r="K15" s="3">
+        <v>40000</v>
+      </c>
+      <c r="L15" s="3">
         <v>179000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>41000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>42000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>30000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>11000</v>
       </c>
       <c r="T15" s="3">
         <v>11000</v>
       </c>
       <c r="U15" s="3">
+        <v>11000</v>
+      </c>
+      <c r="V15" s="3">
         <v>8000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>6000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>6000</v>
       </c>
       <c r="AA15" s="3">
         <v>6000</v>
       </c>
       <c r="AB15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>5000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>6000</v>
       </c>
       <c r="AD15" s="3">
         <v>6000</v>
@@ -1698,34 +1721,37 @@
         <v>6000</v>
       </c>
       <c r="AH15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AI15" s="3">
         <v>5000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>7000</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>6000</v>
       </c>
       <c r="AK15" s="3">
         <v>6000</v>
       </c>
       <c r="AL15" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="AM15" s="3">
         <v>5000</v>
       </c>
       <c r="AN15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>4000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>2000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2448000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2139000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2015000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2200000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2287000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2284000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2215000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2122000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2346000</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2395000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2367000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2368000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2467000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2589000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2292000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1993000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2003000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2007000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1758000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1730000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1631000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1472000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1227000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1110000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1266000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1364000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1326000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1406000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1367000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1397000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1486000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1508000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1353000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1337000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1292000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1301000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1194000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1077000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E18" s="3">
         <v>198000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>189000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>219000</v>
       </c>
-      <c r="G18" s="3">
-        <v>245000</v>
-      </c>
       <c r="H18" s="3">
+        <v>248000</v>
+      </c>
+      <c r="I18" s="3">
         <v>174000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>236000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>302000</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>216000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>202000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>355000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>328000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>264000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>56000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>308000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>483000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>531000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>517000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>536000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>567000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>326000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1611000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>184000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>83000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>194000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>68000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>260000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>186000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>320000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>259000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>374000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>358000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>343000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>240000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>229000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>218000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>170000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>117000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>246000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2053,260 +2086,267 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-48000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-44000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-45000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-36000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-45000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-51000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-76000</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-78000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-86000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-16000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-42000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>42000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>167000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>119000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>120000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>61000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>116000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>117000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>108000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>85000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>91000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>126000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>90000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>86000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>96000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-54000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>118000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>122000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>56000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>92000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>93000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>99000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>68000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E21" s="3">
         <v>286000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>273000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>306000</v>
       </c>
-      <c r="G21" s="3">
-        <v>323000</v>
-      </c>
       <c r="H21" s="3">
+        <v>326000</v>
+      </c>
+      <c r="I21" s="3">
         <v>259000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>327000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>418000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>179000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>335000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>328000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>412000</v>
       </c>
       <c r="O21" s="3">
         <v>412000</v>
       </c>
       <c r="P21" s="3">
+        <v>412000</v>
+      </c>
+      <c r="Q21" s="3">
         <v>320000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>258000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>580000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>709000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>757000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>678000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>746000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>777000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>525000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1688000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>359000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>263000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>406000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>160000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>445000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>358000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>500000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>296000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>582000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>562000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>545000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>375000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>403000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>388000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>341000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>257000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>387000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E22" s="3">
         <v>183000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>177000</v>
       </c>
       <c r="F22" s="3">
         <v>177000</v>
@@ -2315,356 +2355,365 @@
         <v>177000</v>
       </c>
       <c r="H22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="I22" s="3">
         <v>170000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>164000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>169000</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>169000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>178000</v>
       </c>
       <c r="N22" s="3">
         <v>178000</v>
       </c>
       <c r="O22" s="3">
-        <v>182000</v>
+        <v>178000</v>
       </c>
       <c r="P22" s="3">
         <v>182000</v>
       </c>
       <c r="Q22" s="3">
+        <v>182000</v>
+      </c>
+      <c r="R22" s="3">
         <v>168000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>154000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>35000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>30000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>28000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>27000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>28000</v>
       </c>
       <c r="AC22" s="3">
         <v>28000</v>
       </c>
       <c r="AD22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>27000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>33000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>31000</v>
       </c>
       <c r="AG22" s="3">
         <v>31000</v>
       </c>
       <c r="AH22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>30000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>33000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>31000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>32000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>30000</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>29000</v>
       </c>
       <c r="AO22" s="3">
         <v>29000</v>
       </c>
       <c r="AP22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="AQ22" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E23" s="3">
         <v>82000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1360000</v>
       </c>
-      <c r="G23" s="3">
-        <v>130000</v>
-      </c>
       <c r="H23" s="3">
+        <v>133000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-6000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1533000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>180000</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>157000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>132000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>714000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>216000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-70000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>321000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>554000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>616000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>557000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>622000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>660000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>409000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1571000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>241000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>147000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>292000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>41000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>323000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>239000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>385000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>174000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>462000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>442000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>432000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>265000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>289000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>281000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>240000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>156000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>281000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>33000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-77000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>384000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61000</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-575000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-236000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>25000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-840000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>127000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>112000</v>
       </c>
       <c r="T24" s="3">
         <v>112000</v>
       </c>
       <c r="U24" s="3">
+        <v>112000</v>
+      </c>
+      <c r="V24" s="3">
         <v>27000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>102000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>116000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>85000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>117000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>30000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>35000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>65000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>53000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>46000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>72000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>65000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>97000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>65000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>57000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>40000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>56000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-5000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E26" s="3">
         <v>49000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1353000</v>
       </c>
-      <c r="G26" s="3">
-        <v>207000</v>
-      </c>
       <c r="H26" s="3">
+        <v>210000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-15000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1917000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>119000</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>124000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>707000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>950000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>220000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>96000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>770000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>194000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>442000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>504000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>530000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>520000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>544000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>324000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1454000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>211000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>112000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>227000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>44000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>270000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>211000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>339000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>102000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>397000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>345000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>367000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>295000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>232000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>241000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>184000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>161000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E27" s="3">
         <v>44000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1357000</v>
       </c>
-      <c r="G27" s="3">
-        <v>194000</v>
-      </c>
       <c r="H27" s="3">
+        <v>197000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-24000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1925000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>113000</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>121000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>698000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>951000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>220000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>91000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>768000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>192000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>440000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>502000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>528000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>519000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>542000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>323000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1453000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>209000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>110000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>225000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>42000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>268000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>210000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>338000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>100000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>396000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>344000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>365000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>294000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>230000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>239000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>183000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>160000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3151,94 +3209,97 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-6000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-10000</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-5000</v>
       </c>
       <c r="I29" s="3">
         <v>-5000</v>
       </c>
       <c r="J29" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K29" s="3">
         <v>-2000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-6000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>-1000</v>
       </c>
       <c r="R29" s="3">
         <v>-1000</v>
       </c>
       <c r="S29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T29" s="3">
         <v>-6000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-4000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-13000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-4000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-5000</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>-1000</v>
       </c>
       <c r="AF29" s="3">
         <v>-1000</v>
@@ -3247,34 +3308,37 @@
         <v>-1000</v>
       </c>
       <c r="AH29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AI29" s="3">
         <v>5000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-91000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-8000</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
       <c r="AO29" s="3">
         <v>0</v>
       </c>
       <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>48000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>44000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>45000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>36000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>45000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>51000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>76000</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>78000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>86000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>16000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>42000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-42000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-167000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-119000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-120000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-61000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-116000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-117000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-85000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-91000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-86000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-96000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>54000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-118000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-116000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-122000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-93000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-99000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-68000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E33" s="3">
         <v>44000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1357000</v>
       </c>
-      <c r="G33" s="3">
-        <v>194000</v>
-      </c>
       <c r="H33" s="3">
+        <v>197000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-24000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1925000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>113000</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>121000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>698000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>951000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>220000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>91000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>767000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>191000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>434000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>502000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>524000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>506000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>538000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>322000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1453000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>207000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>107000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>218000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>43000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>263000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>209000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>337000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>99000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>401000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>344000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>363000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>203000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>226000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>231000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>183000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>160000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>262000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E35" s="3">
         <v>44000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1357000</v>
       </c>
-      <c r="G35" s="3">
-        <v>194000</v>
-      </c>
       <c r="H35" s="3">
+        <v>197000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-24000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1925000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>113000</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="L35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>121000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>698000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>951000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>220000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>91000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>767000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>191000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>434000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>502000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>524000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>506000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>538000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>322000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1453000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>207000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>107000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>218000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>43000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>263000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>209000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>337000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>99000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>401000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>344000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>363000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>203000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>226000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>231000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>183000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>160000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>262000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4220,130 +4306,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1364000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1758000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1263000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1440000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1173000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>951000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>962000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>813000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1185000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1483000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1805000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1357000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1296000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1167000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1508000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9671000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>783000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>605000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>536000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1340000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1054000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>791000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>955000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>615000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>539000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>570000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>463000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>497000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>491000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>441000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>439000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>703000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>708000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>490000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>576000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>461000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>511000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>501000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>638000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -4389,59 +4479,59 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3" t="s">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>28000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>29000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>331000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>533000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>35000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>36000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>38000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>40000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>26000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>27000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>29000</v>
-      </c>
-      <c r="AG42" s="3">
-        <v>31000</v>
       </c>
       <c r="AH42" s="3">
         <v>31000</v>
       </c>
       <c r="AI42" s="3">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="AJ42" s="3">
         <v>32000</v>
@@ -4450,876 +4540,900 @@
         <v>32000</v>
       </c>
       <c r="AL42" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AM42" s="3">
         <v>31000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>30000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>31000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>30000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1869000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1680000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1467000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1695000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1919000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1880000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1614000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2055000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1926000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1825000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1784000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1909000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1963000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2313000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2054000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1612000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1827000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1913000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1667000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1738000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1788000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1510000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1242000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1063000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1041000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1282000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1303000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1358000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1318000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1365000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1445000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1476000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1230000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1249000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1212000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1102000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1024000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1005000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2305000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2284000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2220000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2213000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2288000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2309000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2284000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2562000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2464000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2354000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2357000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2337000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2514000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2749000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2808000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1723000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1713000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1549000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1524000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1159000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1118000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1025000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>978000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1001000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1031000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1036000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1038000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>994000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1011000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1009000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1046000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>917000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>955000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>900000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>809000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>771000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>717000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>720000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E45" s="3">
         <v>247000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>743000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>742000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>295000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>278000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>266000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>276000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>329000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>283000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>272000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>284000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>479000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>219000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>241000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>186000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>129000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>124000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>70000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>90000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>72000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>53000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>55000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>57000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>62000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>51000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>43000</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>44000</v>
       </c>
       <c r="AE45" s="3">
         <v>44000</v>
       </c>
       <c r="AF45" s="3">
+        <v>44000</v>
+      </c>
+      <c r="AG45" s="3">
         <v>47000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>40000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>48000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>53000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>54000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>63000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>59000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>38000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>60000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>5795000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5969000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5693000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6090000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5675000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5418000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5126000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5706000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5904000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5945000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6218000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5887000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6252000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6448000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6611000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13192000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4459000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4200000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3807000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4355000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4061000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3710000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3763000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2771000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2709000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2855000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2765000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2843000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2876000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2884000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2874000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3180000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3153000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3006000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2792000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2613000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2583000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2389000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2472000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2978000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>1233000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1227000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1252000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1259000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1263000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1220000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1217000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1253000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1215000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1238000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1220000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1245000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1028000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1062000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>954000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>935000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>847000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>823000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>842000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>818000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>796000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>820000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>993000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>957000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>981000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>975000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>970000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>959000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>950000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>979000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>981000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>963000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>979000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>976000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>938000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>885000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>874000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>852000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>864000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>5224000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5314000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5435000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5544000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5691000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5638000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5661000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5852000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5763000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5867000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6006000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5862000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5944000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6002000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5997000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4335000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4422000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4455000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4429000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4155000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4137000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4097000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4171000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4061000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3926000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3879000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3916000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3791000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3851000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3931000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3719000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3699000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3724000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3801000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3762000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3706000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3663000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3571000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3577000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3578000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>7226000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7276000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7355000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7383000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9238000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9083000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9028000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10855000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10743000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10828000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10952000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10935000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11070000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11225000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11247000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1939000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2023000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2111000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2147000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1434000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1447000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1442000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1485000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1445000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1415000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1358000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1386000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1368000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1410000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1407000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1367000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1381000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1394000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1443000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1304000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1298000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1277000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>992000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>990000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>831000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>605000</v>
+      </c>
+      <c r="E52" s="3">
         <v>608000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>601000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>546000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>525000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>543000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>555000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>554000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>579000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>537000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>524000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>535000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>523000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>553000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1355000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>917000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>874000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>813000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>769000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>797000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>757000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>711000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>670000</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>499000</v>
       </c>
       <c r="AA52" s="3">
         <v>499000</v>
       </c>
       <c r="AB52" s="3">
+        <v>499000</v>
+      </c>
+      <c r="AC52" s="3">
         <v>472000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>434000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>442000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>410000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>402000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>374000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>583000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>555000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>551000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>704000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>507000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>475000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>462000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>466000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>21408000</v>
+      </c>
+      <c r="E54" s="3">
         <v>21735000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21695000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22169000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23713000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23197000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22838000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25892000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25812000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26033000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26597000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25538000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25649000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26090000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26272000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21337000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12713000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12426000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11975000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11583000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11220000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10756000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10909000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9769000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9506000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9545000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9476000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9414000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9506000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9574000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9313000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9824000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9789000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9780000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9538000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9062000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8883000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8288000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8357000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>8757000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6016,100 +6146,101 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1485000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1441000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1279000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1248000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1283000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1314000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1228000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1446000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1538000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1447000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1510000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1263000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1243000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1445000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1518000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1128000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1250000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1169000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1160000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1042000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>998000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>906000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>797000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>699000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>599000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>724000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>780000</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>764000</v>
       </c>
       <c r="AE57" s="3">
         <v>764000</v>
       </c>
       <c r="AF57" s="3">
+        <v>764000</v>
+      </c>
+      <c r="AG57" s="3">
         <v>699000</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>819000</v>
       </c>
       <c r="AH57" s="3">
         <v>819000</v>
@@ -6118,638 +6249,656 @@
         <v>819000</v>
       </c>
       <c r="AJ57" s="3">
+        <v>819000</v>
+      </c>
+      <c r="AK57" s="3">
         <v>797000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>807000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>695000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>666000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>615000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>625000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1384000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1817000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1275000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1271000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>330000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>484000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1580000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1690000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2063000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2525000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1472000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1496000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1596000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1474000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1306000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>977000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>809000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>860000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>791000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>103000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>500000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>497000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>496000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>958000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1045000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>749000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>496000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>368000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>319000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>743000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>561000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>229000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>366000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>425000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>326000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>435000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>384000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>107000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>118000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>92000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E59" s="3">
         <v>472000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>536000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>488000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>483000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>438000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>390000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>428000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>403000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>392000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>420000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>363000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>449000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>447000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1244000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>683000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>536000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>525000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>554000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>667000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>631000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>532000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>680000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>752000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>618000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>455000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>478000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>401000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>325000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>380000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>399000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>484000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>425000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>380000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>426000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>420000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>374000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>293000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>334000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>415000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>4006000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4316000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3683000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3727000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2767000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2797000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3890000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4159000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4626000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4925000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4072000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3616000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3922000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3851000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4068000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2788000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2595000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2554000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2505000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1812000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2129000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1935000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1973000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2409000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2262000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1928000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1754000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1533000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1408000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1822000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1779000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1532000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1610000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1602000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1559000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1550000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1424000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1015000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1077000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1098000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>11013000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11088000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11659000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11933000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12984000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12662000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11372000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11649000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11340000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11314000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12626000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12625000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13236000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13755000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13373000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11360000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3022000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3132000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3176000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3724000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3156000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3135000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3227000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3140000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2989000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3356000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3409000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3359000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3444000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2933000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2970000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3196000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3228000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3343000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3315000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2954000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2931000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2851000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2890000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2923000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1022000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1002000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1025000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1059000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1143000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>803000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>694000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>920000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>763000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>803000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>891000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>729000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>777000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>720000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2726000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1895000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1871000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1787000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1757000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1776000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1778000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1779000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1814000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1336000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1386000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1425000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1415000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1383000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1400000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1380000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1185000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1153000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1164000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1170000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1365000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1423000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1406000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1381000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1369000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1585000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>16820000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17250000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17223000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17790000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18009000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17582000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17275000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18174000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18203000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18502000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19045000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18589000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19561000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19960000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20635000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16387000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7833000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7819000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7786000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7664000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7422000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7214000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7383000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7261000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7019000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7097000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6969000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6667000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6642000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6527000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6329000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6283000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6409000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6527000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6651000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6347000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6189000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5677000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5769000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6047000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>10039000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9917000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9876000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9861000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11243000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11076000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11054000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13091000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13051000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12973000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12929000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12308000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11433000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11289000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11274000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10584000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10466000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10106000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9677000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9227000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8797000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8335000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8091000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6710000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6576000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6543000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6399000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6431000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6245000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6114000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5847000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5819000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5491000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5220000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4920000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4781000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4617000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4451000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4320000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4211000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>4167000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4063000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4049000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3954000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5276000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5186000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5129000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7274000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7166000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7071000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7091000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6491000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5624000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5661000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5637000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4950000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4880000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4607000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4189000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3919000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3798000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3542000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3526000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2508000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2487000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2448000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2507000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2747000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2864000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3047000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2984000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3541000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3380000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3253000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2887000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2715000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2694000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2611000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2588000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2710000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E81" s="3">
         <v>44000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1357000</v>
       </c>
-      <c r="G81" s="3">
-        <v>194000</v>
-      </c>
       <c r="H81" s="3">
+        <v>197000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-24000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1925000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>113000</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="L81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>121000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>698000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>951000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>220000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>91000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>767000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>191000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>434000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>502000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>524000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>506000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>538000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>322000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1453000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>207000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>107000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>218000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>43000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>263000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>209000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>337000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>99000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>401000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>344000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>363000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>203000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>226000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>231000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>183000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>160000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>262000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8793,8 +8991,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -8802,121 +9001,124 @@
         <v>151000</v>
       </c>
       <c r="E83" s="3">
+        <v>151000</v>
+      </c>
+      <c r="F83" s="3">
         <v>76000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>225000</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>149000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>152000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>144000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>98000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>178000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>98000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>105000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>107000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>106000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>160000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>105000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>107000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>106000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>94000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>93000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>91000</v>
       </c>
       <c r="Y83" s="3">
         <v>91000</v>
       </c>
       <c r="Z83" s="3">
+        <v>91000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>90000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>89000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>86000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>91000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>95000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>86000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>84000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>91000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>90000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>80000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>79000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>82000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>77000</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>72000</v>
       </c>
       <c r="AO83" s="3">
         <v>72000</v>
       </c>
       <c r="AP83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="AQ83" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E89" s="3">
         <v>76000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>252000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>447000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>410000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>37000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>494000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>79000</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>101000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>830000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>403000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>762000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-96000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>541000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>467000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>495000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>316000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>584000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>630000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>427000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>116000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>274000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>431000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>379000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>259000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>326000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>397000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>424000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>307000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>363000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>467000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>585000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>143000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>58000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>255000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>298000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>192000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-47000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>304000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-84000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-93000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-102000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-105000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-88000</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-137000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-128000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-131000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-145000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-164000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-143000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-139000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-124000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-137000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-163000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-102000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-110000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-92000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-85000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-88000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-119000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-144000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-65000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-79000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-79000</v>
       </c>
       <c r="AI91" s="3">
         <v>-79000</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-87000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-64000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-54000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-58000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E94" s="3">
         <v>425000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-104000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-59000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-98000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-128000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100000</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-151000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-168000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>375000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-163000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10713000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-143000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-136000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-149000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1286000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-108000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>177000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>98000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>979000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-78000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-128000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-168000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-82000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-177000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-98000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-78000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-96000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-235000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-92000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-68000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-325000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-64000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-247000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10223,8 +10456,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -10232,10 +10466,10 @@
         <v>3000</v>
       </c>
       <c r="E96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F96" s="3">
         <v>4000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>3000</v>
       </c>
       <c r="G96" s="3">
         <v>3000</v>
@@ -10244,22 +10478,22 @@
         <v>3000</v>
       </c>
       <c r="I96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J96" s="3">
         <v>77000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>76000</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="L96" s="3">
-        <v>77000</v>
       </c>
       <c r="M96" s="3">
         <v>77000</v>
       </c>
       <c r="N96" s="3">
-        <v>76000</v>
+        <v>77000</v>
       </c>
       <c r="O96" s="3">
         <v>76000</v>
@@ -10268,85 +10502,88 @@
         <v>76000</v>
       </c>
       <c r="Q96" s="3">
+        <v>76000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-77000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-73000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-74000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-73000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-76000</v>
       </c>
       <c r="W96" s="3">
         <v>-76000</v>
       </c>
       <c r="X96" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-78000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-72000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-73000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-74000</v>
       </c>
       <c r="AB96" s="3">
         <v>-74000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-75000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-77000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-78000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-71000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-73000</v>
       </c>
       <c r="AI96" s="3">
         <v>-73000</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-63000</v>
+        <v>-73000</v>
       </c>
       <c r="AK96" s="3">
         <v>-63000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-62000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-65000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-51000</v>
       </c>
       <c r="AO96" s="3">
         <v>-51000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-52000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-546000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-324000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-118000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-116000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>45000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-189000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-376000</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-259000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-240000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-700000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-447000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1944000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8600000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-159000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-95000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-99000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-228000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-344000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-371000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-933000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-290000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-232000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-199000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-299000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-307000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-130000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-526000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-383000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-254000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>145000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-247000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>21000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-270000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-292000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E101" s="3">
         <v>5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-28000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>25000</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>26000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>65000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-36000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-22000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>65000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-36000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-22000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-3000</v>
       </c>
       <c r="U101" s="3">
         <v>-3000</v>
       </c>
       <c r="V101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W101" s="3">
         <v>-8000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>20000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>13000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>8000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>10000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>16000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>5000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-394000</v>
+      </c>
+      <c r="E102" s="3">
         <v>495000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-177000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>267000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>222000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>149000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-372000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-322000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>448000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>129000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-341000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8163000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8888000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>178000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-804000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>286000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>263000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-164000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>340000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>76000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>107000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>50000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-264000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-86000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>115000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-50000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>10000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-137000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-614000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>517000</v>
       </c>
     </row>
